--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_encounters_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_encounters_SOURCE.xlsx
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.52</v>
+        <v>1.56</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -499,19 +499,19 @@
         <v>123</v>
       </c>
       <c r="F3">
-        <v>5.03</v>
+        <v>4.14</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
       <c r="J3">
-        <v>14172</v>
+        <v>22900</v>
       </c>
       <c r="K3">
         <v>35784</v>
@@ -520,13 +520,13 @@
         <v>1.56</v>
       </c>
       <c r="M3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>1.51</v>
       </c>
       <c r="O3">
-        <v>2.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>2.7</v>
+        <v>1.74</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -597,19 +597,19 @@
         <v>123</v>
       </c>
       <c r="F5">
-        <v>5.16</v>
+        <v>4.34</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>13241</v>
+        <v>20512</v>
       </c>
       <c r="K5">
         <v>35784</v>
@@ -618,13 +618,13 @@
         <v>1.74</v>
       </c>
       <c r="M5">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N5">
-        <v>2.61</v>
+        <v>1.69</v>
       </c>
       <c r="O5">
-        <v>2.79</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
